--- a/sheet/FG.xlsx
+++ b/sheet/FG.xlsx
@@ -4,17 +4,15 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13965" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13965" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Reel" sheetId="1" r:id="rId1"/>
     <sheet name="Reel_FG" sheetId="3" r:id="rId2"/>
     <sheet name="PayTable" sheetId="2" r:id="rId3"/>
     <sheet name="FreeSpins" sheetId="4" r:id="rId4"/>
+    <sheet name="Game" sheetId="5" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="16">
   <si>
     <t>R1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -70,6 +68,18 @@
   </si>
   <si>
     <t>S</t>
+  </si>
+  <si>
+    <t>Setting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WindowHeight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -114,7 +124,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,6 +134,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCFE7D5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -141,7 +157,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -160,6 +176,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1"/>
@@ -176,23 +198,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="主遊戲"/>
-      <sheetName val="免費遊戲"/>
-      <sheetName val="Summary"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1363,4 +1368,44 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
+    <col min="2" max="5" width="9.140625" style="3"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="9"/>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="K4" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>